--- a/VerveStacks_POL_grids_syn_5/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_syn_5/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0BB87A2-F29A-4E47-883A-85FEB982BC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F567F5C0-9DF4-4C06-941C-3BAE28021612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9C990B8B-F2F9-4F50-9056-D037C42FAFDC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{585DFC4C-ADB7-4D2A-A21F-772905B2CDA6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3661,7 +3661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0D3913-DC96-472B-92A6-2AD3EA2943AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFF1CE3-7BD1-4A79-8FF8-F0C6B371D810}">
   <dimension ref="B9:T187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13647,7 +13647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EBC0DAA-544E-4623-B5AB-7D44FD38477A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8088B8-3E65-4864-8866-DF3B2BB2EC44}">
   <dimension ref="B9:T151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20462,7 +20462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66432C4E-A9BF-4208-9F67-3AAE9BC31538}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88276A17-EAF9-43A1-ACC7-4A9B01D05A9D}">
   <dimension ref="B9:T374"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31576,7 +31576,7 @@
         <v>238</v>
       </c>
       <c r="P220" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q220" t="s">
         <v>323</v>
@@ -31632,7 +31632,7 @@
         <v>238</v>
       </c>
       <c r="P221" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q221" t="s">
         <v>323</v>
@@ -32136,7 +32136,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q230" t="s">
         <v>323</v>
@@ -32192,7 +32192,7 @@
         <v>254</v>
       </c>
       <c r="P231" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q231" t="s">
         <v>323</v>
@@ -33200,7 +33200,7 @@
         <v>287</v>
       </c>
       <c r="P249" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q249" t="s">
         <v>323</v>
@@ -33256,7 +33256,7 @@
         <v>287</v>
       </c>
       <c r="P250" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q250" t="s">
         <v>323</v>
@@ -34022,7 +34022,7 @@
         <v>33</v>
       </c>
       <c r="L264">
-        <v>0.32007950711570909</v>
+        <v>0.32007950711570904</v>
       </c>
       <c r="N264" t="s">
         <v>321</v>
@@ -34069,7 +34069,7 @@
         <v>33</v>
       </c>
       <c r="L265">
-        <v>0.32007950711570909</v>
+        <v>0.32007950711570904</v>
       </c>
       <c r="N265" t="s">
         <v>321</v>
@@ -34116,7 +34116,7 @@
         <v>33</v>
       </c>
       <c r="L266">
-        <v>0.32007950711570909</v>
+        <v>0.32007950711570904</v>
       </c>
       <c r="N266" t="s">
         <v>321</v>
@@ -37947,7 +37947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4FB2C44-20D6-4336-9253-7FAF89615EAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6528E6-8C2B-4ADF-8565-19DF91A9403A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_syn_5/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_syn_5/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F567F5C0-9DF4-4C06-941C-3BAE28021612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D704BD52-8128-4B78-B79D-1735AD8CBEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{585DFC4C-ADB7-4D2A-A21F-772905B2CDA6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A1806062-45FC-43B7-A482-A9FB21AFA569}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -83,144 +83,144 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G100000201421</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G100000201422</t>
+  </si>
+  <si>
+    <t>e_gen3</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G1000002499</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G1000002500</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G1000002501</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G1000002502</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_G100001017887</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_gen0</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_gen0__ember</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_gen1__ember</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_gen2</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_gen2__ember</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_gen3__ember</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966</t>
+  </si>
+  <si>
     <t>e_gen4</t>
   </si>
   <si>
-    <t>ep_bioenergy_G100000201421</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_G100000201422</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_G1000002499</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_G1000002500</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_G1000002501</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_G1000002502</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_G100001017887</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_gen1</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_gen1__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_gen2</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_gen2__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_gen3__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_gen4__ember</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102967</t>
   </si>
   <si>
@@ -1049,13 +1049,13 @@
     <t>yes</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - gen0_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - gen1_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - gen2_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - gen4_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>Bedzin power station_Unit 1 -- operating</t>
@@ -3661,7 +3661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFF1CE3-7BD1-4A79-8FF8-F0C6B371D810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA9F700-0611-4F58-9BDD-149FD4F87A90}">
   <dimension ref="B9:T187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13647,7 +13647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8088B8-3E65-4864-8866-DF3B2BB2EC44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0ADCE8-1F0A-4F7A-984D-C3658E29E5A6}">
   <dimension ref="B9:T151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13773,7 +13773,7 @@
         <v>540</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>2033</v>
@@ -19371,7 +19371,7 @@
         <v>178</v>
       </c>
       <c r="D120" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="E120">
         <v>2027</v>
@@ -20462,7 +20462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88276A17-EAF9-43A1-ACC7-4A9B01D05A9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4D56B4-D92A-4C98-949D-AF7AF0734881}">
   <dimension ref="B9:T374"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20962,16 +20962,16 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="F19">
-        <v>0.04</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G19">
-        <v>0.29354999999999998</v>
+        <v>0.27398000000000006</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -21015,13 +21015,13 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>2022</v>
       </c>
       <c r="F20">
-        <v>7.4480587618048266E-2</v>
+        <v>0.16864533053515213</v>
       </c>
       <c r="G20">
         <v>0.322905</v>
@@ -21068,25 +21068,25 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="F21">
-        <v>3.6999999999999998E-2</v>
+        <v>0.22769779643231899</v>
       </c>
       <c r="G21">
-        <v>0.27398000000000006</v>
+        <v>0.322905</v>
       </c>
       <c r="H21">
-        <v>5197.5</v>
+        <v>4427.5</v>
       </c>
       <c r="I21">
-        <v>185.9</v>
+        <v>157.30000000000004</v>
       </c>
       <c r="J21">
-        <v>10.08</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K21">
         <v>50</v>
@@ -21098,7 +21098,7 @@
         <v>27</v>
       </c>
       <c r="P21" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q21" t="s">
         <v>323</v>
@@ -21121,25 +21121,25 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="F22">
-        <v>0.16864533053515213</v>
+        <v>0.04</v>
       </c>
       <c r="G22">
-        <v>0.322905</v>
+        <v>0.29354999999999998</v>
       </c>
       <c r="H22">
-        <v>4427.5</v>
+        <v>5197.5</v>
       </c>
       <c r="I22">
-        <v>157.30000000000001</v>
+        <v>185.9</v>
       </c>
       <c r="J22">
-        <v>9.240000000000002</v>
+        <v>10.08</v>
       </c>
       <c r="K22">
         <v>50</v>
@@ -21151,7 +21151,7 @@
         <v>28</v>
       </c>
       <c r="P22" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Q22" t="s">
         <v>323</v>
@@ -21174,25 +21174,25 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>2022</v>
       </c>
       <c r="F23">
-        <v>3.6176285414480584E-2</v>
+        <v>7.4480587618048266E-2</v>
       </c>
       <c r="G23">
-        <v>0.31312000000000001</v>
+        <v>0.322905</v>
       </c>
       <c r="H23">
-        <v>5197.5</v>
+        <v>4427.5</v>
       </c>
       <c r="I23">
-        <v>185.9</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J23">
-        <v>10.08</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K23">
         <v>50</v>
@@ -21204,7 +21204,7 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q23" t="s">
         <v>323</v>
@@ -21227,25 +21227,25 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>2022</v>
       </c>
       <c r="F24">
-        <v>0.22769779643231899</v>
+        <v>3.6176285414480584E-2</v>
       </c>
       <c r="G24">
-        <v>0.322905</v>
+        <v>0.31312000000000001</v>
       </c>
       <c r="H24">
-        <v>4427.5</v>
+        <v>5197.5</v>
       </c>
       <c r="I24">
-        <v>157.30000000000004</v>
+        <v>185.9</v>
       </c>
       <c r="J24">
-        <v>9.240000000000002</v>
+        <v>10.08</v>
       </c>
       <c r="K24">
         <v>50</v>
@@ -21257,7 +21257,7 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="Q24" t="s">
         <v>323</v>
@@ -30652,7 +30652,7 @@
         <v>213</v>
       </c>
       <c r="D202" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E202">
         <v>1942</v>
@@ -30705,13 +30705,13 @@
         <v>213</v>
       </c>
       <c r="D203" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="E203">
         <v>2022</v>
       </c>
       <c r="F203">
-        <v>7.9599918755163937E-2</v>
+        <v>8.0526478656017697E-2</v>
       </c>
       <c r="G203">
         <v>0.33123000000000002</v>
@@ -30749,13 +30749,13 @@
         <v>213</v>
       </c>
       <c r="D204" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E204">
         <v>2022</v>
       </c>
       <c r="F204">
-        <v>0.18868128890112931</v>
+        <v>2.0889714128339315E-2</v>
       </c>
       <c r="G204">
         <v>0.33123000000000002</v>
@@ -30793,13 +30793,13 @@
         <v>213</v>
       </c>
       <c r="D205" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E205">
         <v>2022</v>
       </c>
       <c r="F205">
-        <v>1.6678078215367681E-2</v>
+        <v>0.12483288846047932</v>
       </c>
       <c r="G205">
         <v>0.33123000000000002</v>
@@ -30837,13 +30837,13 @@
         <v>213</v>
       </c>
       <c r="D206" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="E206">
         <v>2022</v>
       </c>
       <c r="F206">
-        <v>2.0889714128339315E-2</v>
+        <v>7.9599918755163937E-2</v>
       </c>
       <c r="G206">
         <v>0.33123000000000002</v>
@@ -31249,7 +31249,7 @@
         <v>33</v>
       </c>
       <c r="L214">
-        <v>0.13965121408677153</v>
+        <v>0.1396512140867715</v>
       </c>
       <c r="N214" t="s">
         <v>321</v>
@@ -31296,7 +31296,7 @@
         <v>33</v>
       </c>
       <c r="L215">
-        <v>0.13965121408677153</v>
+        <v>0.1396512140867715</v>
       </c>
       <c r="N215" t="s">
         <v>321</v>
@@ -31343,7 +31343,7 @@
         <v>33</v>
       </c>
       <c r="L216">
-        <v>0.13965121408677153</v>
+        <v>0.1396512140867715</v>
       </c>
       <c r="N216" t="s">
         <v>321</v>
@@ -31576,7 +31576,7 @@
         <v>238</v>
       </c>
       <c r="P220" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q220" t="s">
         <v>323</v>
@@ -31632,7 +31632,7 @@
         <v>238</v>
       </c>
       <c r="P221" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q221" t="s">
         <v>323</v>
@@ -32136,7 +32136,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q230" t="s">
         <v>323</v>
@@ -32192,7 +32192,7 @@
         <v>254</v>
       </c>
       <c r="P231" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q231" t="s">
         <v>323</v>
@@ -34022,7 +34022,7 @@
         <v>33</v>
       </c>
       <c r="L264">
-        <v>0.32007950711570904</v>
+        <v>0.32007950711570909</v>
       </c>
       <c r="N264" t="s">
         <v>321</v>
@@ -34069,7 +34069,7 @@
         <v>33</v>
       </c>
       <c r="L265">
-        <v>0.32007950711570904</v>
+        <v>0.32007950711570909</v>
       </c>
       <c r="N265" t="s">
         <v>321</v>
@@ -34116,7 +34116,7 @@
         <v>33</v>
       </c>
       <c r="L266">
-        <v>0.32007950711570904</v>
+        <v>0.32007950711570909</v>
       </c>
       <c r="N266" t="s">
         <v>321</v>
@@ -37947,7 +37947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6528E6-8C2B-4ADF-8565-19DF91A9403A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD7B006-7137-40E5-A0ED-281C0313C1B9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_syn_5/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_syn_5/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D704BD52-8128-4B78-B79D-1735AD8CBEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A90AC3A9-9FEC-4E2A-8165-E340FECCC809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A1806062-45FC-43B7-A482-A9FB21AFA569}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{556D5835-8959-4E55-974E-52D80A7B6FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3661,7 +3661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA9F700-0611-4F58-9BDD-149FD4F87A90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00810CE5-E9C0-496A-960A-82B70E9CC91E}">
   <dimension ref="B9:T187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13647,7 +13647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0ADCE8-1F0A-4F7A-984D-C3658E29E5A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C36FC1-2A68-4480-B2D8-2C20876A804B}">
   <dimension ref="B9:T151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20462,7 +20462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4D56B4-D92A-4C98-949D-AF7AF0734881}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668043DA-297F-4070-8B07-E9ABA214D0C8}">
   <dimension ref="B9:T374"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31576,7 +31576,7 @@
         <v>238</v>
       </c>
       <c r="P220" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q220" t="s">
         <v>323</v>
@@ -31632,7 +31632,7 @@
         <v>238</v>
       </c>
       <c r="P221" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q221" t="s">
         <v>323</v>
@@ -32136,7 +32136,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q230" t="s">
         <v>323</v>
@@ -32192,7 +32192,7 @@
         <v>254</v>
       </c>
       <c r="P231" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q231" t="s">
         <v>323</v>
@@ -32304,7 +32304,7 @@
         <v>257</v>
       </c>
       <c r="P233" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q233" t="s">
         <v>323</v>
@@ -32360,7 +32360,7 @@
         <v>257</v>
       </c>
       <c r="P234" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q234" t="s">
         <v>323</v>
@@ -33200,7 +33200,7 @@
         <v>287</v>
       </c>
       <c r="P249" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="Q249" t="s">
         <v>323</v>
@@ -33256,7 +33256,7 @@
         <v>287</v>
       </c>
       <c r="P250" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="Q250" t="s">
         <v>323</v>
@@ -37947,7 +37947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD7B006-7137-40E5-A0ED-281C0313C1B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7983525B-FD91-4954-ACE8-8970487DDA20}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
